--- a/artfynd/A 11828-2023 artfynd.xlsx
+++ b/artfynd/A 11828-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 11828-2023 artfynd.xlsx
+++ b/artfynd/A 11828-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>103995709</v>
+        <v>103997433</v>
       </c>
       <c r="B2" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>552726.0543954446</v>
+        <v>552544</v>
       </c>
       <c r="R2" t="n">
-        <v>7018793.554079575</v>
+        <v>7018806</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -740,7 +735,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>Ragunda</t>
+          <t>Borgvattnet</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -750,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>08:44</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>08:44</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,12 +794,7 @@
         <v>103995778</v>
       </c>
       <c r="B3" t="n">
-        <v>77177</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -836,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>552699.8285554571</v>
+        <v>552700</v>
       </c>
       <c r="R3" t="n">
-        <v>7018799.422733131</v>
+        <v>7018799</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -917,15 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>103997359</v>
+        <v>103997375</v>
       </c>
       <c r="B4" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -933,21 +918,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -957,10 +942,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>552554.567867608</v>
+        <v>552701</v>
       </c>
       <c r="R4" t="n">
-        <v>7018811.442006753</v>
+        <v>7018759</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -992,7 +977,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>08:39</t>
+          <t>08:29</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1002,7 +987,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>08:39</t>
+          <t>08:29</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1013,11 +998,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Tall</t>
-        </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
@@ -1043,37 +1023,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>103997433</v>
+        <v>103997359</v>
       </c>
       <c r="B5" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1083,10 +1058,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>552543.8394086353</v>
+        <v>552555</v>
       </c>
       <c r="R5" t="n">
-        <v>7018806.317822548</v>
+        <v>7018812</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1118,7 +1093,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>08:44</t>
+          <t>08:39</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1128,7 +1103,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>08:44</t>
+          <t>08:39</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1139,6 +1114,11 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Tall</t>
+        </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
@@ -1167,12 +1147,7 @@
         <v>103997400</v>
       </c>
       <c r="B6" t="n">
-        <v>77258</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1204,10 +1179,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>552550.8839087711</v>
+        <v>552551</v>
       </c>
       <c r="R6" t="n">
-        <v>7018816.3306461</v>
+        <v>7018816</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1285,15 +1260,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>103995720</v>
+        <v>103995709</v>
       </c>
       <c r="B7" t="n">
-        <v>77259</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1301,21 +1271,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1325,10 +1295,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>552722.9680355482</v>
+        <v>552726</v>
       </c>
       <c r="R7" t="n">
-        <v>7018789.454379548</v>
+        <v>7018794</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1399,6 +1369,238 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>103995720</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Anders-Persmyran, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>552723</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7018790</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2022-07-21</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>08:25</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2022-07-21</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>08:25</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>103995797</v>
+      </c>
+      <c r="B9" t="n">
+        <v>95765</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>1004672</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Källmossor</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Philonotis</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Brid.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Anders-Persmyran, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>552524</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7018768</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Borgvattnet</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2022-07-21</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>08:46</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2022-07-21</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>08:46</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
         <is>
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>

--- a/artfynd/A 11828-2023 artfynd.xlsx
+++ b/artfynd/A 11828-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,6 +793,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103997433</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -904,6 +914,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103995778</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1020,6 +1035,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103997375</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1141,6 +1161,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103997359</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1257,6 +1282,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103997400</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1373,6 +1403,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103995709</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1489,6 +1524,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103995720</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1605,8 +1645,23 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103995797</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>